--- a/Dic_Einheiten.xlsx
+++ b/Dic_Einheiten.xlsx
@@ -435,7 +435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="20.0390625"/>
@@ -1609,12 +1609,12 @@
     <row outlineLevel="0" r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>E_NUMPLSTK</t>
+          <t>E_NUMKUM</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Anzahl der Müllteile aus Plastik pro 100 m Küstenlinie</t>
+          <t>Kumulierte Anzahl</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Number of pieces of platic waste per 100 meters of beach length</t>
+          <t>Cumulative number</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -1636,12 +1636,12 @@
     <row outlineLevel="0" r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>E_P10H3EWN</t>
+          <t>E_NUMPLSTK</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Je 100 Einwohner/-innen</t>
+          <t>Anzahl der Müllteile aus Plastik pro 100 m Küstenlinie</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Per 100 inhabitants</t>
+          <t>Number of pieces of platic waste per 100 meters of beach length</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -1663,12 +1663,12 @@
     <row outlineLevel="0" r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>E_P10H4EWN</t>
+          <t>E_P10H3EWN</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Je 1 000 Einwohner/-innen</t>
+          <t>Je 100 Einwohner/-innen</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Per 1,000 inhabitants</t>
+          <t>Per 100 inhabitants</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -1690,12 +1690,12 @@
     <row outlineLevel="0" r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>E_P10H4FGA</t>
+          <t>E_P10H4EWN</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Je 1 000 Frauen gleichen Alters</t>
+          <t>Je 1 000 Einwohner/-innen</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Per 1,000 women of same age</t>
+          <t>Per 1,000 inhabitants</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -1717,12 +1717,12 @@
     <row outlineLevel="0" r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>E_P10H4LGB</t>
+          <t>E_P10H4FGA</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Je 1 000 Lebendgeborene</t>
+          <t>Je 1 000 Frauen gleichen Alters</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Per 1,000 live births</t>
+          <t>Per 1,000 women of same age</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -1744,12 +1744,12 @@
     <row outlineLevel="0" r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>E_P10H5EWN</t>
+          <t>E_P10H4LGB</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Je 10 000 Einwohner/-innen</t>
+          <t>Je 1 000 Lebendgeborene</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Per 10,000 inhabitants</t>
+          <t>Per 1,000 live births</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -1771,12 +1771,12 @@
     <row outlineLevel="0" r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>E_P10H6ERW</t>
+          <t>E_P10H5EWN</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Je 100 000 Erwachsene</t>
+          <t>Je 10 000 Einwohner/-innen</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Per 100,000 adults</t>
+          <t>Per 10,000 inhabitants</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -1798,12 +1798,12 @@
     <row outlineLevel="0" r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>E_P10H6EWN</t>
+          <t>E_P10H6ERW</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Je 100 000 Einwohner/-innen</t>
+          <t>Je 100 000 Erwachsene</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Per 100,000 inhabitants</t>
+          <t>Per 100,000 adults</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -1825,7 +1825,7 @@
     <row outlineLevel="0" r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>E_P10H6EWN_1</t>
+          <t>E_P10H6EWN</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>'Per 100,000 inhabitants '</t>
+          <t>Per 100,000 inhabitants</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -1852,12 +1852,12 @@
     <row outlineLevel="0" r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>E_P10H6EWN_F</t>
+          <t>E_P10H6EWN_1</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Je 100 000 Einwohnerinnen</t>
+          <t>Je 100 000 Einwohner/-innen</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Per 100,000 female inhabitants</t>
+          <t>'Per 100,000 inhabitants '</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -1879,7 +1879,7 @@
     <row outlineLevel="0" r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>E_P10H6EWN_F_1</t>
+          <t>E_P10H6EWN_F</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>'Per 100,000 female inhabitants '</t>
+          <t>Per 100,000 female inhabitants</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -1906,12 +1906,12 @@
     <row outlineLevel="0" r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>E_P10H6LGB</t>
+          <t>E_P10H6EWN_F_1</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Je 100 000 Lebendgeborene</t>
+          <t>Je 100 000 Einwohnerinnen</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Per 100,000 live births</t>
+          <t>'Per 100,000 female inhabitants '</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -1933,12 +1933,12 @@
     <row outlineLevel="0" r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>E_P10H6MA</t>
+          <t>E_P10H6LGB</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Je 100 000 Mitarbeiter/-innen</t>
+          <t>Je 100 000 Lebendgeborene</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Per 100,000 employees</t>
+          <t>Per 100,000 live births</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -1960,12 +1960,12 @@
     <row outlineLevel="0" r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>E_PH</t>
+          <t>E_P10H6MA</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>pH-Wert</t>
+          <t>Je 100 000 Mitarbeiter/-innen</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>pH-value</t>
+          <t>Per 100,000 employees</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -1987,61 +1987,61 @@
     <row outlineLevel="0" r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>E_PRMIOEW</t>
+          <t>E_PH</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Je 1 Million Einwohner/-innen</t>
+          <t>pH-Wert</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Je 1 Mill.  Einwohner/-innen</t>
+          <t/>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Per 1 million inhabitants</t>
+          <t>pH-value</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Per 1 mn inhabitants</t>
+          <t/>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>E_PRZNT</t>
+          <t>E_PRMIOEW</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Prozent</t>
+          <t>Je 1 Million Einwohner/-innen</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>Je 1 Mill.  Einwohner/-innen</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Percentage</t>
+          <t>Per 1 million inhabitants</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>Per 1 mn inhabitants</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>E_PRZNT_1</t>
+          <t>E_PRZNT</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>'Percentage '</t>
+          <t>Percentage</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -2068,214 +2068,241 @@
     <row outlineLevel="0" r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>E_PRZNTBIP</t>
+          <t>E_PRZNT_1</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Prozent des BIP</t>
+          <t>Prozent</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t/>
+          <t>%</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Percent of GDP</t>
+          <t>'Percentage '</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t/>
+          <t>%</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>E_QK</t>
+          <t>E_PRZNTBIP</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>km²</t>
+          <t>Prozent des BIP</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>km²</t>
+          <t/>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>km²</t>
+          <t>Percent of GDP</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>km²</t>
+          <t/>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>E_T</t>
+          <t>E_QK</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Tonnen</t>
+          <t>km²</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>km²</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Tonnes</t>
+          <t>km²</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>km²</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>E_TM3</t>
+          <t>E_T</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>1 000 m³</t>
+          <t>Tonnen</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t/>
+          <t>t</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1 000 m³</t>
+          <t>Tonnes</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t/>
+          <t>t</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>E_TPK</t>
+          <t>E_TM3</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Tonnen pro Kopf</t>
+          <t>1 000 m³</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>t/Kopf</t>
+          <t/>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Tonnes per capita</t>
+          <t>1 000 m³</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>t/capita</t>
+          <t/>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>E_TT</t>
+          <t>E_TPK</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>1 000 Tonnen</t>
+          <t>Tonnen pro Kopf</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>1 000 t</t>
+          <t>t/Kopf</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>1,000 tonnes</t>
+          <t>Tonnes per capita</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>1,000 t</t>
+          <t>t/capita</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>E_WPK</t>
+          <t>E_TT</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Watt pro Kopf</t>
+          <t>1 000 Tonnen</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>W/Kopf</t>
+          <t>1 000 t</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Watts per capita</t>
+          <t>1,000 tonnes</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>W/capita</t>
+          <t>1,000 t</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
+          <t>E_WPK</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Watt pro Kopf</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>W/Kopf</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Watts per capita</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>W/capita</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
           <t>E_YEARS</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>Jahre</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D69" s="4" t="inlineStr">
         <is>
           <t>Years</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="E69" s="4" t="inlineStr">
         <is>
           <t>a</t>
         </is>
